--- a/Reports/DailyScrum/反省・改善・目標.xlsx
+++ b/Reports/DailyScrum/反省・改善・目標.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Desktop\Ticket‘ｓフォルダー\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\DailyScrum\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>反省点</t>
     <rPh sb="0" eb="3">
@@ -145,43 +145,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・β版の時はややこしいところは２人で協力する。
-・しっかり確認を取る。(情報理解)
-・優先順位を考えて制作する。
-・</t>
-    <rPh sb="2" eb="3">
-      <t>バン</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ニン</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>キョウリョク</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="36" eb="40">
-      <t>ジョウホウリカイ</t>
-    </rPh>
-    <rPh sb="43" eb="47">
-      <t>ユウセンジュンイ</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>カンガ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>セイサク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <r>
       <t>・</t>
     </r>
@@ -255,12 +218,211 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <r>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ゲームループがしっかり動くようにする。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+・ゲームに音声をつける
+・NPCの実装①
+・車の実装②</t>
+    </r>
+    <rPh sb="12" eb="13">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>オンセイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>クルマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・β版の時はややこしいところは２人で協力する。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>〇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+・しっかり確認を取る。(情報理解)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+・優先順位を考えて制作する。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>〇</t>
+    </r>
+    <rPh sb="2" eb="3">
+      <t>バン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ニン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>キョウリョク</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="37" eb="41">
+      <t>ジョウホウリカイ</t>
+    </rPh>
+    <rPh sb="45" eb="49">
+      <t>ユウセンジュンイ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・確認が不十分(GitHub)
+→上書き保存で消されている。
+・仕事の分担がうまく出来ていない。
+→大本ができていないのに違う仕事を行っている。</t>
+    <rPh sb="1" eb="3">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>フジュウブン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ウワガ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>シゴト</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ブンタン</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>デキ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>オオモト</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>シゴト</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・グレープみんなで確認を取る。
+・朝のデイリースクラムでjiraに沿ってミーティングを進めるようにする。</t>
+    <rPh sb="9" eb="11">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>アサ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ソ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>スス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,6 +441,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
       <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -312,10 +482,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -607,13 +777,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
@@ -630,19 +800,28 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="87" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
